--- a/product_upload/packages/40/file.xlsx
+++ b/product_upload/packages/40/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -836,6 +841,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>INCRESYNC 25/45 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-59A9596414F8</t>
         </is>
       </c>
@@ -859,7 +869,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1028,6 +1038,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>INCRESYNC 25/15 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-2AA827B79E36</t>
         </is>
       </c>
@@ -1051,7 +1066,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1210,6 +1225,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-7463B0F09F45</t>
         </is>
       </c>
@@ -1233,7 +1253,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1398,6 +1418,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>INCRESYNC 25/30 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-4E17BEB4EA0B</t>
         </is>
       </c>
@@ -1421,7 +1446,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1584,6 +1609,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>PENTASA XTEND 2 GM SACHET</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-F2FC75FB1770</t>
         </is>
       </c>
@@ -1607,7 +1637,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1778,6 +1808,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t xml:space="preserve">COXICEL 200 MG HARD CAPSULE </t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-7B82C8AD040E</t>
         </is>
       </c>
@@ -1801,7 +1836,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1964,6 +1999,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>EZEACT PLUS 40MG/25MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-502514D23704</t>
         </is>
       </c>
@@ -1987,7 +2027,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2154,6 +2194,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>BUFOMIX 160/4.5MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-A386A3544D84</t>
         </is>
       </c>
@@ -2177,7 +2222,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2332,6 +2377,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>BUFOMIX 320/9MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-32F1954045D1</t>
         </is>
       </c>
@@ -2355,7 +2405,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2524,6 +2574,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>VIPIDIA 12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-322877ACA523</t>
         </is>
       </c>
@@ -2547,7 +2602,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2716,6 +2771,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>VIPIDIA 25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-94F65D17002A</t>
         </is>
       </c>
@@ -2739,7 +2799,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2904,6 +2964,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>EDARBYCLOR 40 MG/12.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-984509444075</t>
         </is>
       </c>
@@ -2927,7 +2992,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3090,6 +3155,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-A4CF473E6430</t>
         </is>
       </c>
@@ -3113,7 +3183,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3278,6 +3348,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>EDARBYCLOR 40 MG/25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-B74ED2CE930D</t>
         </is>
       </c>
@@ -3301,7 +3376,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3460,6 +3535,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>LAYAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-5E2789B01C40</t>
         </is>
       </c>
@@ -3483,7 +3563,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3642,6 +3722,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>CYERO 25/15 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-78395F7B0B88</t>
         </is>
       </c>
@@ -3665,7 +3750,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3836,6 +3921,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>STRATTERA 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-CF2169449655</t>
         </is>
       </c>
@@ -3859,7 +3949,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4032,6 +4122,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>EDARBI 40 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-5906263E3908</t>
         </is>
       </c>
@@ -4055,7 +4150,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4228,6 +4323,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>EDARBI 80 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-AF6FD0C8921A</t>
         </is>
       </c>
@@ -4251,7 +4351,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4414,6 +4514,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CYERO 25/30 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-ADC68E8B7954</t>
         </is>
       </c>
@@ -4437,7 +4542,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4608,6 +4713,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>VEMLIDY 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-32E0569B7D17</t>
         </is>
       </c>
@@ -4631,7 +4741,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>ROMACIN POWDER FOR ORAL/RECTAL Suspension</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-77933A0D2B59</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4990,6 +5105,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>DIOZAD</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-B8FB997036C2</t>
         </is>
       </c>
@@ -5013,7 +5133,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5172,6 +5292,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>CORREX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9E23A3591CF4</t>
         </is>
       </c>
@@ -5195,7 +5320,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5366,6 +5491,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>ISONIAZID 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-B5DBA57485E3</t>
         </is>
       </c>
@@ -5389,7 +5519,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5548,6 +5678,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LATUDA 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-95024E534F5D</t>
         </is>
       </c>
@@ -5571,7 +5706,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5730,6 +5865,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>XOROLA 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-4CE46A91A759</t>
         </is>
       </c>
@@ -5753,7 +5893,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5916,6 +6056,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CAVERTA 50 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-952FD453C7CB</t>
         </is>
       </c>
@@ -5939,7 +6084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6102,6 +6247,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>LUTTAGEN 0.075MG/0.03MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-C596EB8B32AF</t>
         </is>
       </c>
@@ -6125,7 +6275,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6298,6 +6448,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>APROVASC 300MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-77E864503D11</t>
         </is>
       </c>
@@ -6321,7 +6476,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6484,6 +6639,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-18068B8A9E7E</t>
         </is>
       </c>
@@ -6507,7 +6667,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6674,6 +6834,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Vislube GEL</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-9A338023AE08</t>
         </is>
       </c>
@@ -6697,7 +6862,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6864,6 +7029,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>TRAVOCORT CREAM</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-A428C6D90DBB</t>
         </is>
       </c>
@@ -6887,7 +7057,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7050,6 +7220,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CO-OLMEPRESS 40 mg/25 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-64FE917E57CC</t>
         </is>
       </c>
@@ -7073,7 +7248,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7232,6 +7407,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ANGINET 160 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-795F7426D6C4</t>
         </is>
       </c>
@@ -7255,7 +7435,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7430,6 +7610,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>TRIX 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-DE1DD09A3E44</t>
         </is>
       </c>
@@ -7453,7 +7638,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7612,6 +7797,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ZYTERO PLUS 12.5 mg/ 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-A1C8EC4AA5D7</t>
         </is>
       </c>
@@ -7635,7 +7825,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7798,6 +7988,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-F30D4ED19F65</t>
         </is>
       </c>
@@ -7821,7 +8016,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7980,6 +8175,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>ANGINET 80 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-0E33DF05E5A8</t>
         </is>
       </c>
@@ -8003,7 +8203,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8170,6 +8370,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>QUZAL 25 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-745001B7FE1E</t>
         </is>
       </c>
@@ -8193,7 +8398,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8352,6 +8557,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>ZYTERO PLUS 12.5 mg/ 1000 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-1EE1D8343E6C</t>
         </is>
       </c>
@@ -8375,7 +8585,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8542,6 +8752,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>DIPROLENE 0.05% OINT</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-0344A2589C96</t>
         </is>
       </c>
@@ -8565,7 +8780,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8728,6 +8943,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>HAIRAL 2% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-5BF20C48021C</t>
         </is>
       </c>
@@ -8751,7 +8971,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8910,6 +9130,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>VELTASSA 25.2G SACHET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-7CD5C31C5B9E</t>
         </is>
       </c>
@@ -8933,7 +9158,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9094,6 +9319,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>CANDEZA 8 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-2D9E66EB7070</t>
         </is>
       </c>
@@ -9117,7 +9347,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9278,6 +9508,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>CANDEZA 16 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-FF9B26FCF934</t>
         </is>
       </c>
@@ -9301,7 +9536,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9470,6 +9705,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>CEBO 200 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-F7735153BB54</t>
         </is>
       </c>
@@ -9493,7 +9733,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9658,6 +9898,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>CANDEZA 16/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-E54A71AF83B7</t>
         </is>
       </c>
@@ -9681,7 +9926,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9846,6 +10091,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>CANDEZA 8/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-90F78F2F1711</t>
         </is>
       </c>
@@ -9869,7 +10119,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10032,6 +10282,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>QUZAL 100 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-C657BEA23624</t>
         </is>
       </c>
@@ -10055,7 +10310,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10218,6 +10473,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>PADO 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-BE64C8B19E51</t>
         </is>
       </c>
@@ -10241,7 +10501,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10400,6 +10660,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>COVATEL 40MG/10MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-EB6AF4C3E71F</t>
         </is>
       </c>
@@ -10423,7 +10688,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10590,6 +10855,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rinvoq </t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-54CBE7C35A9E</t>
         </is>
       </c>
@@ -10613,7 +10883,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10772,6 +11042,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>COVATEL</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-DAD63DC1863C</t>
         </is>
       </c>
@@ -10795,7 +11070,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10962,6 +11237,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>QUZAL 200 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-0416DDD51455</t>
         </is>
       </c>
@@ -10985,7 +11265,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11148,6 +11428,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>GAVILDA 50MG TABLET     28S</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-05390CDC0BB8</t>
         </is>
       </c>
@@ -11171,7 +11456,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11334,6 +11619,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>GAVILDA 50MG TABLET      56S</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-FF4EB0307049</t>
         </is>
       </c>
@@ -11357,7 +11647,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11520,6 +11810,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>GLADOS MET 15/850 TABLETS</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B3A7BF889D43</t>
         </is>
       </c>
@@ -11543,7 +11838,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11706,6 +12001,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>GLADOS MET 15/500 TABLETS</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-0AE43D4C519E</t>
         </is>
       </c>
@@ -11729,7 +12029,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11888,6 +12188,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Relif 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-73ACAF97AB46</t>
         </is>
       </c>
@@ -11911,7 +12216,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12070,6 +12375,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Relif 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-7038B888D2B9</t>
         </is>
       </c>
@@ -12093,7 +12403,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12264,6 +12574,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>IMATOX 4MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-9E341CEC8FC3</t>
         </is>
       </c>
@@ -12287,7 +12602,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12452,6 +12767,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>EZORA 40 MG GASTRO-RESISTANT HARD CAPSULES (14S)</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-8E66642E34A6</t>
         </is>
       </c>
@@ -12475,7 +12795,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12642,6 +12962,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>IMATOX 8MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-C333C3FD6731</t>
         </is>
       </c>
@@ -12665,7 +12990,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12834,6 +13159,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>EZORA 40 MG GASTRO-RESISTANT HARD CAPSULES (28S)</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-2DD436F4B19A</t>
         </is>
       </c>
@@ -12857,7 +13187,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13016,6 +13346,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t xml:space="preserve">NIZORTAN PLUS </t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-1673621D10C6</t>
         </is>
       </c>
@@ -13039,7 +13374,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13204,6 +13539,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>EZORA 20 MG GASTRO-RESISTANT HARD CAPSULES (14S)</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-47134A029562</t>
         </is>
       </c>
@@ -13227,7 +13567,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13386,6 +13726,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-85E7BC2976BF</t>
         </is>
       </c>
@@ -13409,7 +13754,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13582,6 +13927,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>EZORA 20 MG GASTRO-RESISTANT HARD CAPSULES (28S)</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-7BFFCDF95832</t>
         </is>
       </c>
@@ -13605,7 +13955,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13764,6 +14114,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-04BD56979378</t>
         </is>
       </c>
@@ -13787,7 +14142,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13942,6 +14297,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>REDUVASC 150MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-322C63FDD2AC</t>
         </is>
       </c>
@@ -13965,7 +14325,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14132,6 +14492,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Pneumovax 23 Pneumococcal Vaccine Polyvalent</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-5942EADC2786</t>
         </is>
       </c>
@@ -14155,7 +14520,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14318,6 +14683,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>REDUVASC 150MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-BDFB69406C8D</t>
         </is>
       </c>
@@ -14341,7 +14711,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14500,6 +14870,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>REDUVASC 300MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-800CEEF476CC</t>
         </is>
       </c>
@@ -14523,7 +14898,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14686,6 +15061,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>REDUVASC 300MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-3E6B2A7D5010</t>
         </is>
       </c>
@@ -14709,7 +15089,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14864,6 +15244,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-E6CB036DBCE8</t>
         </is>
       </c>
@@ -14887,7 +15272,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15052,6 +15437,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>CELLONA 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-F4C322367B77</t>
         </is>
       </c>
@@ -15075,7 +15465,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15242,6 +15632,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-13989DEF3001</t>
         </is>
       </c>
@@ -15265,7 +15660,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15428,6 +15823,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>BANORIV 2.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-1053898DA8AE</t>
         </is>
       </c>
@@ -15451,7 +15851,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15610,6 +16010,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>BANORIV 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-E90C39760AB0</t>
         </is>
       </c>
@@ -15633,7 +16038,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15796,6 +16201,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>BANORIV 15MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-07CBC72836DD</t>
         </is>
       </c>
@@ -15819,7 +16229,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15982,6 +16392,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>BANORIV 20 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D8BA328E5979</t>
         </is>
       </c>
@@ -16005,7 +16420,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16168,6 +16583,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>ZANSOR 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-3A8C1E01EFD2</t>
         </is>
       </c>
@@ -16191,7 +16611,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16346,6 +16766,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>PERTENSIO 125 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-F43AA518559A</t>
         </is>
       </c>
@@ -16369,7 +16794,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16528,6 +16953,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>BENZAFLEX XR 15 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-D2E54F543068</t>
         </is>
       </c>
@@ -16551,7 +16981,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16718,6 +17148,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>DEBROMU 40MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-BD582011DA64</t>
         </is>
       </c>
@@ -16741,7 +17176,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16904,6 +17339,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>BENZAFLEX XR 30 mg Capsule</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-A6044685E33D</t>
         </is>
       </c>
@@ -16927,7 +17367,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17098,6 +17538,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>OLFEN PATCHES</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-5C8AE5BC1F90</t>
         </is>
       </c>
@@ -17121,7 +17566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17280,6 +17725,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-A8B7F91DD111</t>
         </is>
       </c>
@@ -17303,7 +17753,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17462,6 +17912,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>EZOLOC 25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-07C05A7C2C3C</t>
         </is>
       </c>
@@ -17485,7 +17940,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17648,6 +18103,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-0DEE75E27ADF</t>
         </is>
       </c>
@@ -17671,7 +18131,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17838,6 +18298,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>QUZAL 300 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-4538BF06B3A3</t>
         </is>
       </c>
@@ -17861,7 +18326,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18028,6 +18493,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>STRATTERA 18MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-7FE628A9D0D7</t>
         </is>
       </c>
@@ -18051,7 +18521,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18214,6 +18684,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ZANSOR 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-3A23593B8EA5</t>
         </is>
       </c>
@@ -18237,7 +18712,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18396,6 +18871,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-E18C699CE9A6</t>
         </is>
       </c>
@@ -18419,7 +18899,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18582,6 +19062,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-1E776DAF126B</t>
         </is>
       </c>
@@ -18605,7 +19090,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18768,6 +19253,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>QATPEN 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-DBCD4608D39B</t>
         </is>
       </c>
@@ -18791,7 +19281,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18954,6 +19444,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>BRIVIACT 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-15734B8A2B1C</t>
         </is>
       </c>
@@ -18977,7 +19472,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19144,6 +19639,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>SODANOR POWDER FOR ORAL/RECTAL SUSP.</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-761B1D8FD0FA</t>
         </is>
       </c>
@@ -19167,7 +19667,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19331,6 +19831,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>DIOZAD</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-A8EF98391B07</t>
         </is>
@@ -19347,7 +19852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19393,100 +19898,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19518,7 +20028,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19533,92 +20043,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-60124</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>446.96</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>364</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19650,7 +20165,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19665,92 +20180,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-22338</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>338.39</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>365</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19782,7 +20302,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19797,92 +20317,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-77319</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>353.96</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>366</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19914,7 +20439,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19929,92 +20454,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-37338</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>72.73999999999999</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>367</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20046,7 +20576,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20061,92 +20591,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-98876</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>123.67</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>368</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20178,7 +20713,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20193,92 +20728,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-93758</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>299.89</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>369</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20310,7 +20850,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20325,92 +20865,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-67472</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>291.52</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>370</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20442,7 +20987,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20457,92 +21002,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-86232</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>29.4</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>371</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20574,7 +21124,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20589,92 +21139,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-52453</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>343.74</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>372</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20706,7 +21261,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20721,92 +21276,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-74197</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>472.62</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>373</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20838,7 +21398,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20853,92 +21413,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-84803</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>72.61</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>374</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20955,7 +21520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21061,6 +21626,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21096,7 +21671,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21161,6 +21736,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-853B520E1EC3</t>
         </is>
@@ -21197,7 +21782,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21262,6 +21847,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1CEBB0CFFF5E</t>
         </is>
@@ -21298,7 +21893,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21363,6 +21958,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-6D7DDB915439</t>
         </is>
@@ -21399,7 +22004,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21464,6 +22069,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-C011E0E1E28F</t>
         </is>
@@ -21500,7 +22115,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21565,6 +22180,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-95C643AE06B4</t>
         </is>
@@ -21601,7 +22226,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21666,6 +22291,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-675E1A54B1D9</t>
         </is>
@@ -21702,7 +22337,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21767,6 +22402,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-183079CFCB6D</t>
         </is>
@@ -21803,7 +22448,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21868,6 +22513,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-EB9C2DE76E2E</t>
         </is>
@@ -21904,7 +22559,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21969,6 +22624,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-8EC95BCE5EE2</t>
         </is>
@@ -22005,7 +22670,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22070,6 +22735,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-FA97A3C429BB</t>
         </is>
@@ -22106,7 +22781,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22171,6 +22846,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-7F2EE3121024</t>
         </is>
@@ -22207,7 +22892,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22272,6 +22957,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-F48646339160</t>
         </is>
@@ -22308,7 +23003,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22373,6 +23068,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-3B83BEEA63A2</t>
         </is>
@@ -22409,7 +23114,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22474,6 +23179,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-DD19B42374D8</t>
         </is>
@@ -22510,7 +23225,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22575,6 +23290,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-17F33F7E9590</t>
         </is>
@@ -22611,7 +23336,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22676,6 +23401,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-AE176B4147B0</t>
         </is>
@@ -22712,7 +23447,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22777,6 +23512,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-C533C5F8C01D</t>
         </is>
@@ -22813,7 +23558,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22878,6 +23623,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-1671B9C194F8</t>
         </is>
@@ -22914,7 +23669,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22979,6 +23734,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-237204F5072F</t>
         </is>
@@ -23015,7 +23780,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23080,6 +23845,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-79AC663A81A3</t>
         </is>

--- a/product_upload/packages/40/file.xlsx
+++ b/product_upload/packages/40/file.xlsx
@@ -686,8 +686,16 @@
           <t>6610197531-137-938243870064</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ INCRESYNC 25/45 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>INCRESYNC 25/45 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1074,8 +1082,16 @@
           <t>3869008582-203-215621781052</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>AXE BRAND UNIVERSAL OIL detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1454,8 +1470,16 @@
           <t>5765478802-688-047742071748</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTASA XTEND 2 GM SACHET</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PENTASA XTEND 2 GM SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1844,8 +1868,16 @@
           <t>9239555223-158-053688109778</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZEACT PLUS 40MG/25MG TABLET</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>EZEACT PLUS 40MG/25MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2230,8 +2262,16 @@
           <t>1940409694-503-592677048739</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BUFOMIX 320/9MCG EASYHALER</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>BUFOMIX 320/9MCG EASYHALER detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -3000,8 +3040,16 @@
           <t>9428837740-894-984928250362</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 40 mg/12.5 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3384,8 +3432,16 @@
           <t>9996077604-004-120937254033</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAYAL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LAYAL 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3571,8 +3627,16 @@
           <t>9106545263-636-147345268320</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYERO 25/15 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>CYERO 25/15 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3758,8 +3822,16 @@
           <t>7700975932-935-574410091648</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 10MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>STRATTERA 10MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4359,8 +4431,16 @@
           <t>5726720732-435-030875945124</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CYERO 25/30 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>CYERO 25/30 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4944,8 +5024,16 @@
           <t>1331512106-742-873972055403</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOZAD</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>DIOZAD detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>
@@ -5141,8 +5229,16 @@
           <t>4285392187-252-087936866493</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CORREX 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CORREX 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5527,8 +5623,16 @@
           <t>6095509204-350-123269843751</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LATUDA 20 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>LATUDA 20 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5714,8 +5818,16 @@
           <t>0018572028-941-137009490994</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XOROLA 2.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>XOROLA 2.5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5901,8 +6013,16 @@
           <t>5619566560-546-127208802817</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAVERTA 50 MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CAVERTA 50 MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6484,8 +6604,16 @@
           <t>9482977911-670-038790493034</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARBAGLU 200MG DISPERSIBLE TABLETS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CARBAGLU 200MG DISPERSIBLE TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -7065,8 +7193,16 @@
           <t>2144104659-040-290575171154</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-OLMEPRESS 40 mg/25 mg F.C. Tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CO-OLMEPRESS 40 mg/25 mg F.C. Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7256,8 +7392,16 @@
           <t>6573239891-875-291770069922</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANGINET 160 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ANGINET 160 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7646,8 +7790,16 @@
           <t>9742185152-255-316358383573</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO PLUS 12.5 mg/ 500 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ZYTERO PLUS 12.5 mg/ 500 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7833,8 +7985,16 @@
           <t>3138481803-379-980082136867</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PENTASA 4GM PROLONGED RELEASE GRANULES IN SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8024,8 +8184,16 @@
           <t>9363913454-813-132744921658</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ANGINET 80 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ANGINET 80 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8211,8 +8379,16 @@
           <t>8136333600-582-270073965191</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 25 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>QUZAL 25 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8406,8 +8582,16 @@
           <t>7382202931-740-859849182488</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZYTERO PLUS 12.5 mg/ 1000 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>ZYTERO PLUS 12.5 mg/ 1000 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8788,8 +8972,16 @@
           <t>5294833719-588-498410564335</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HAIRAL 2% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>HAIRAL 2% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8979,8 +9171,16 @@
           <t>7139398563-787-877789566074</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VELTASSA 25.2G SACHET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>VELTASSA 25.2G SACHET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9166,8 +9366,16 @@
           <t>1169382439-328-005800626378</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 8 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>CANDEZA 8 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -9355,8 +9563,16 @@
           <t>1037893566-983-463026674566</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 16 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CANDEZA 16 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -9741,8 +9957,16 @@
           <t>7413341820-209-015163595505</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 16/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>CANDEZA 16/12.5 mg TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -9934,8 +10158,16 @@
           <t>9156751702-902-428900180861</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEZA 8/12.5 mg TABLETS</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>CANDEZA 8/12.5 mg TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -10127,8 +10359,16 @@
           <t>3710331646-944-047316482027</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 100 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>QUZAL 100 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10318,8 +10558,16 @@
           <t>5673676005-775-830410109218</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PADO 20MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PADO 20MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10509,8 +10757,16 @@
           <t>7448872790-754-015245025046</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL 40MG/10MG TABLET</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>COVATEL 40MG/10MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10891,8 +11147,16 @@
           <t>3085493019-567-369834697864</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVATEL</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>COVATEL detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11078,8 +11342,16 @@
           <t>1558099005-335-783520944565</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 200 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>QUZAL 200 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11273,8 +11545,16 @@
           <t>4104019774-109-652220444326</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVILDA 50MG TABLET     28S</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>GAVILDA 50MG TABLET     28S detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11464,8 +11744,16 @@
           <t>8424925439-221-314407756612</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GAVILDA 50MG TABLET      56S</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>GAVILDA 50MG TABLET      56S detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11655,8 +11943,16 @@
           <t>0877182219-745-282514558303</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLADOS MET 15/850 TABLETS</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>GLADOS MET 15/850 TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11846,8 +12142,16 @@
           <t>9097108439-746-410668312403</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLADOS MET 15/500 TABLETS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>GLADOS MET 15/500 TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12037,8 +12341,16 @@
           <t>5874240949-645-808216361795</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Relif 100 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Relif 100 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12224,8 +12536,16 @@
           <t>0728998844-039-481125176897</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Relif 200 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Relif 200 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12610,8 +12930,16 @@
           <t>7186687280-102-599158306623</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZORA 40 MG GASTRO-RESISTANT HARD CAPSULES (14S)</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>EZORA 40 MG GASTRO-RESISTANT HARD CAPSULES (14S) detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -13195,8 +13523,16 @@
           <t>0951313027-911-493533829256</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13382,8 +13718,16 @@
           <t>2386833837-274-127734026225</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZORA 20 MG GASTRO-RESISTANT HARD CAPSULES (14S)</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>EZORA 20 MG GASTRO-RESISTANT HARD CAPSULES (14S) detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -13575,8 +13919,16 @@
           <t>8428515136-062-367243411343</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13963,8 +14315,16 @@
           <t>1991771846-601-278992384008</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NIZORTAN PLUS</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>NIZORTAN PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14150,8 +14510,16 @@
           <t>3989126476-494-517596922052</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REDUVASC 150MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>REDUVASC 150MG/5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14333,8 +14701,16 @@
           <t>2106344855-801-525991867501</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pneumovax 23 Pneumococcal Vaccine Polyvalent</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Pneumovax 23 Pneumococcal Vaccine Polyvalent detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14528,8 +14904,16 @@
           <t>5831176046-463-836591992938</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REDUVASC 150MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>REDUVASC 150MG/10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14719,8 +15103,16 @@
           <t>3641352882-245-828564456006</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REDUVASC 300MG/5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>REDUVASC 300MG/5MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14906,8 +15298,16 @@
           <t>9417940258-191-065767713576</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REDUVASC 300MG/10MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>REDUVASC 300MG/10MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15097,8 +15497,16 @@
           <t>0140164851-917-941086335665</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AXE BRAND UNIVERSAL OIL</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>AXE BRAND UNIVERSAL OIL detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15280,8 +15688,16 @@
           <t>5172210914-895-948171762244</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CELLONA 500 mg F.C.TAB</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>CELLONA 500 mg F.C.TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -15473,8 +15889,16 @@
           <t>7053374893-859-216132565198</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15668,8 +16092,16 @@
           <t>3711051019-024-735622166486</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANORIV 2.5 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>BANORIV 2.5 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15859,8 +16291,16 @@
           <t>6980011447-733-049130322603</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANORIV 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>BANORIV 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16046,8 +16486,16 @@
           <t>1599151523-780-873611741597</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANORIV 15MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>BANORIV 15MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16237,8 +16685,16 @@
           <t>9716018034-414-769261962713</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BANORIV 20 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>BANORIV 20 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16428,8 +16884,16 @@
           <t>2893362089-621-426411480304</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZANSOR 150MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>ZANSOR 150MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16619,8 +17083,16 @@
           <t>7946088070-000-794873919455</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PERTENSIO 125 mg Film-Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>PERTENSIO 125 mg Film-Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16802,8 +17274,16 @@
           <t>7016364339-972-179117225049</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BENZAFLEX XR 15 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>BENZAFLEX XR 15 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -17184,8 +17664,16 @@
           <t>2192708925-838-853688067431</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BENZAFLEX XR 30 mg Capsule</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>BENZAFLEX XR 30 mg Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17574,8 +18062,16 @@
           <t>4622634258-648-159032058414</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>SNAFI 20MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17761,8 +18257,16 @@
           <t>9988139894-791-937017270063</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EZOLOC 25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>EZOLOC 25 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17948,8 +18452,16 @@
           <t>4082259799-525-919873857026</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EMIFLOC 500 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>EMIFLOC 500 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18139,8 +18651,16 @@
           <t>1048703970-871-279583654891</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 300 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>QUZAL 300 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18334,8 +18854,16 @@
           <t>4355429231-295-449558133233</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STRATTERA 18MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>STRATTERA 18MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18529,8 +19057,16 @@
           <t>2189422354-246-612752618357</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZANSOR 300MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ZANSOR 300MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18720,8 +19256,16 @@
           <t>6320176454-495-651825107821</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 20 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>GLOFEL 20 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18907,8 +19451,16 @@
           <t>7920388906-195-403950414914</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QUZAL 400 mg Tablets</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>QUZAL 400 mg Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -19098,8 +19650,16 @@
           <t>9842949132-853-013585151997</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ QATPEN 25MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>QATPEN 25MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19289,8 +19849,16 @@
           <t>1882514638-685-529915294130</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BRIVIACT 50MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>BRIVIACT 50MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -19675,8 +20243,16 @@
           <t>3585819663-195-062027666518</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIOZAD</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>DIOZAD detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">Razy Al Madina Pharmaceutical	</t>

--- a/product_upload/packages/40/file.xlsx
+++ b/product_upload/packages/40/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20474,7 +20474,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22096,7 +22096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22177,40 +22177,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22290,38 +22295,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>78.54000000000001</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-853B520E1EC3</t>
         </is>
@@ -22401,38 +22411,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>58.19</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1CEBB0CFFF5E</t>
         </is>
@@ -22512,38 +22527,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>481.26</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-6D7DDB915439</t>
         </is>
@@ -22623,38 +22643,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>133.9</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-C011E0E1E28F</t>
         </is>
@@ -22734,38 +22759,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>158.26</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-95C643AE06B4</t>
         </is>
@@ -22845,38 +22875,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>380.07</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-675E1A54B1D9</t>
         </is>
@@ -22956,38 +22991,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>329.13</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-183079CFCB6D</t>
         </is>
@@ -23067,38 +23107,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>425.67</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-EB9C2DE76E2E</t>
         </is>
@@ -23178,38 +23223,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>172.05</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-8EC95BCE5EE2</t>
         </is>
@@ -23289,38 +23339,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>95.18000000000001</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-FA97A3C429BB</t>
         </is>
@@ -23400,38 +23455,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>288.11</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-7F2EE3121024</t>
         </is>
@@ -23511,38 +23571,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>169.76</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-F48646339160</t>
         </is>
@@ -23622,38 +23687,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>454.97</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-3B83BEEA63A2</t>
         </is>
@@ -23733,38 +23803,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>238.2</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-DD19B42374D8</t>
         </is>
@@ -23844,38 +23919,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>413.45</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-17F33F7E9590</t>
         </is>
@@ -23955,38 +24035,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>353.15</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-AE176B4147B0</t>
         </is>
@@ -24066,38 +24151,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>365.46</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-C533C5F8C01D</t>
         </is>
@@ -24177,38 +24267,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>407.92</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-1671B9C194F8</t>
         </is>
@@ -24288,38 +24383,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>118.03</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-237204F5072F</t>
         </is>
@@ -24399,38 +24499,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>408.25</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-79AC663A81A3</t>
         </is>
